--- a/kahoot/orientation/history/9_finnish_history__0006.xlsx
+++ b/kahoot/orientation/history/9_finnish_history__0006.xlsx
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Att bevara goda levnadsförhållanden för nuvarande och framtida generationer</t>
+          <t>Att bevara goda livsvillkor för nuvarande och framtida generationer</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
